--- a/CharityAI_TestResults.xlsx
+++ b/CharityAI_TestResults.xlsx
@@ -1060,7 +1060,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generated: June 11, 2026  10:51   |   Framework: Selenium WebDriver + pytest   |   App: http://localhost:5173</t>
+          <t>Generated: June 12, 2026  14:35   |   Framework: Selenium WebDriver + pytest   |   App: http://localhost:5173</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       <c r="J2" s="24" t="inlineStr"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       <c r="J3" s="27" t="inlineStr"/>
       <c r="K3" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       <c r="J4" s="24" t="inlineStr"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       <c r="J5" s="27" t="inlineStr"/>
       <c r="K5" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       <c r="J6" s="24" t="inlineStr"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       <c r="J7" s="27" t="inlineStr"/>
       <c r="K7" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       <c r="J8" s="24" t="inlineStr"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       <c r="J9" s="27" t="inlineStr"/>
       <c r="K9" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       <c r="J10" s="24" t="inlineStr"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="J11" s="27" t="inlineStr"/>
       <c r="K11" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       <c r="J12" s="24" t="inlineStr"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       <c r="J13" s="27" t="inlineStr"/>
       <c r="K13" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       <c r="J14" s="24" t="inlineStr"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K15" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       <c r="J16" s="24" t="inlineStr"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       <c r="J17" s="27" t="inlineStr"/>
       <c r="K17" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       <c r="J18" s="24" t="inlineStr"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       <c r="J19" s="27" t="inlineStr"/>
       <c r="K19" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       <c r="J20" s="30" t="inlineStr"/>
       <c r="K20" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       <c r="J21" s="27" t="inlineStr"/>
       <c r="K21" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       <c r="J22" s="30" t="inlineStr"/>
       <c r="K22" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       <c r="J23" s="27" t="inlineStr"/>
       <c r="K23" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       <c r="J24" s="30" t="inlineStr"/>
       <c r="K24" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       <c r="J25" s="27" t="inlineStr"/>
       <c r="K25" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       <c r="J26" s="30" t="inlineStr"/>
       <c r="K26" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       <c r="J27" s="27" t="inlineStr"/>
       <c r="K27" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       <c r="J28" s="30" t="inlineStr"/>
       <c r="K28" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       <c r="J29" s="27" t="inlineStr"/>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       <c r="J30" s="30" t="inlineStr"/>
       <c r="K30" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       <c r="J31" s="27" t="inlineStr"/>
       <c r="K31" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       <c r="J32" s="30" t="inlineStr"/>
       <c r="K32" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       <c r="J33" s="27" t="inlineStr"/>
       <c r="K33" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       <c r="J34" s="30" t="inlineStr"/>
       <c r="K34" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       <c r="J35" s="27" t="inlineStr"/>
       <c r="K35" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       <c r="J36" s="30" t="inlineStr"/>
       <c r="K36" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       <c r="J37" s="27" t="inlineStr"/>
       <c r="K37" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       <c r="J38" s="30" t="inlineStr"/>
       <c r="K38" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       <c r="J39" s="27" t="inlineStr"/>
       <c r="K39" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       <c r="J40" s="30" t="inlineStr"/>
       <c r="K40" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       <c r="J41" s="27" t="inlineStr"/>
       <c r="K41" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       <c r="J42" s="33" t="inlineStr"/>
       <c r="K42" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       <c r="J43" s="27" t="inlineStr"/>
       <c r="K43" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       <c r="J44" s="33" t="inlineStr"/>
       <c r="K44" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       <c r="J45" s="27" t="inlineStr"/>
       <c r="K45" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="J46" s="33" t="inlineStr"/>
       <c r="K46" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3713,7 @@
       <c r="J47" s="27" t="inlineStr"/>
       <c r="K47" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       <c r="J48" s="33" t="inlineStr"/>
       <c r="K48" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       <c r="J49" s="27" t="inlineStr"/>
       <c r="K49" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       <c r="J50" s="33" t="inlineStr"/>
       <c r="K50" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       <c r="J51" s="27" t="inlineStr"/>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       <c r="J52" s="33" t="inlineStr"/>
       <c r="K52" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       <c r="J53" s="27" t="inlineStr"/>
       <c r="K53" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       <c r="J54" s="36" t="inlineStr"/>
       <c r="K54" s="36" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       <c r="J55" s="27" t="inlineStr"/>
       <c r="K55" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       <c r="J56" s="36" t="inlineStr"/>
       <c r="K56" s="36" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       <c r="J57" s="27" t="inlineStr"/>
       <c r="K57" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       <c r="J58" s="36" t="inlineStr"/>
       <c r="K58" s="36" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       <c r="J59" s="27" t="inlineStr"/>
       <c r="K59" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       <c r="J60" s="36" t="inlineStr"/>
       <c r="K60" s="36" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       <c r="J61" s="27" t="inlineStr"/>
       <c r="K61" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="K62" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="K63" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="J64" s="30" t="inlineStr"/>
       <c r="K64" s="30" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="K65" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="K66" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       <c r="J67" s="27" t="inlineStr"/>
       <c r="K67" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       <c r="J68" s="24" t="inlineStr"/>
       <c r="K68" s="24" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       <c r="J69" s="27" t="inlineStr"/>
       <c r="K69" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       <c r="J70" s="33" t="inlineStr"/>
       <c r="K70" s="33" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       <c r="J71" s="27" t="inlineStr"/>
       <c r="K71" s="27" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51</t>
+          <t>2026-06-12 14:35</t>
         </is>
       </c>
     </row>
